--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -2212,16 +2212,8 @@
         </is>
       </c>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Cool-to-touch Breeze cover</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Noticeably cooler on contact than standard TEMPUR models.</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
           <t>Hybrid coil base</t>
@@ -2252,16 +2244,8 @@
         </is>
       </c>
       <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>Funda Breeze fresca al tacto</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Notablemente más fresco al contacto que los modelos TEMPUR estándar.</t>
-        </is>
-      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
           <t>Base híbrida de resortes</t>
@@ -4670,7 +4654,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Marvelous Middle|Plush|Side Sleeper</t>
+          <t>Marvelous Middle|Plush</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -4708,12 +4692,12 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>High-density foam rails give a bigger usable sleep surface than value plush beds.</t>
+          <t>High-density foam rails reinforce the mattress perimeter.</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>Marvelous Middle|Suave|Para Dormir de Lado</t>
+          <t>Marvelous Middle|Suave</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr"/>
@@ -4740,7 +4724,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>Rieles de espuma de alta densidad dan más superficie útil que las camas suaves de valor.</t>
+          <t>Rieles de espuma de alta densidad refuerzan el perímetro del colchón.</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -2163,11 +2163,7 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Cooling adaptive hybrid</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>1</v>
       </c>
@@ -2208,22 +2204,14 @@
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Cool-to-the-touch Breeze cover and Pure Cool material over a hybrid coil base — cooling plus true TEMPUR pressure relief.</t>
+          <t>A hybrid build.</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Hybrid coil base</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Adds airflow and a touch of responsiveness under the memory foam.</t>
-        </is>
-      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
           <t>Frescura|Híbrido|Medio</t>
@@ -2240,22 +2228,14 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Funda Breeze fresca al tacto y material Pure Cool sobre una base híbrida de resortes — frescura más el verdadero alivio de presión TEMPUR.</t>
+          <t>Una construcción híbrida.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>Base híbrida de resortes</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>Agrega ventilación y un toque de respuesta bajo la espuma viscoelástica.</t>
-        </is>
-      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -7003,7 +7003,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"pricing":{"schemaVersion":1,"enabled":false,"displayEnabled":false,"currency":"USD","authority":{"owner":"","role":""},"freshness":{"status":"unapproved","maxAgeDays":null,"approvedBy":"","approvedAt":null},"sourcePolicy":{"status":"unapproved","allowedSourceHosts":[],"approvedBy":"","approvedAt":null},"purchaseAssessment":{"policy":"runtime-transaction-amount"},"sizes":["twin","twin_xl","full","queen","king","cal_king"],"surfaces":{"drawer":false,"sleepSystem":false,"results":false,"handoff":false,"sleepPlan":false},"presentation":{"status":"unapproved","approvals":{"business":{"status":"unapproved","by":"","at":null},"legal":{"status":"unapproved","by":"","at":null},"nativeReview":{"status":"pending","by":"","at":null}},"assumptions":[],"disclosures":[],"states":{}},"products":[],"formulas":[]}}</t>
+          <t>{"pricing":{"schemaVersion":1,"enabled":false,"displayEnabled":false,"currency":"USD","authority":{"owner":"","role":""},"freshness":{"status":"unapproved","maxAgeDays":null,"approvedBy":"","approvedAt":null},"sourcePolicy":{"status":"unapproved","allowedSourceHosts":[],"approvedBy":"","approvedAt":null},"purchaseAssessment":{"policy":"runtime-transaction-amount"},"sizes":["twin","twin_xl","full","queen","king","cal_king"],"surfaces":{"drawer":false,"sleepSystem":false,"results":false,"handoff":false,"sleepPlan":false,"compare":false},"presentation":{"status":"unapproved","approvals":{"business":{"status":"unapproved","by":"","at":null},"legal":{"status":"unapproved","by":"","at":null},"nativeReview":{"status":"pending","by":"","at":null}},"assumptions":[],"disclosures":[],"states":{}},"products":[],"formulas":[]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6911,7 +6911,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"promotions":{"schemaVersion":1,"activeScenario":null,"allowedSourceHosts":["lacks.com"],"scenarios":{}},"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","surfaces":{"drawer":false,"sleepSystem":false},"allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"paymentPreferenceLabel":{"en":"Payment preference","es":"Preferencia de pago"},"preferenceNone":{"en":"Not selected","es":"Sin seleccionar"},"optionsExploredLabel":{"en":"Options explored","es":"Opciones exploradas"},"reviewOption":{"en":"Review this option","es":"Revisar esta opción"},"hideDetails":{"en":"Hide details","es":"Ocultar detalles"},"considerOption":{"en":"Consider this option","es":"Considerar esta opción"},"currentlyConsidering":{"en":"Currently considering ✓","es":"En consideración ✓"},"clearPreference":{"en":"Clear preference","es":"Quitar preferencia"},"preferenceNotNow":{"en":"Not right now","es":"Ahora no"},"exploreConsequence":{"en":"Explore options together. Nothing is submitted and no application is started.","es":"Exploren las opciones juntos. No se envía nada y no se inicia ninguna solicitud."},"sheetDone":{"en":"Done","es":"Listo"},"preferenceNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"preferenceClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
+          <t>{"promotions":{"schemaVersion":1,"activeScenario":null,"allowedSourceHosts":["lacks.com"],"scenarios":{}},"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","surfaces":{"drawer":false,"sleepSystem":false},"allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"paymentPreferenceLabel":{"en":"Payment preference","es":"Preferencia de pago"},"preferenceNone":{"en":"Not selected","es":"Sin seleccionar"},"hideDetails":{"en":"Hide details","es":"Ocultar detalles"},"considerOption":{"en":"Consider this option","es":"Considerar esta opción"},"currentlyConsidering":{"en":"Currently considering ✓","es":"En consideración ✓"},"clearPreference":{"en":"Clear preference","es":"Quitar preferencia"},"preferenceNotNow":{"en":"Not choosing a payment option today","es":"Hoy no elegimos una forma de pago"},"exploreConsequence":{"en":"Explore options together. Nothing is submitted and no application is started.","es":"Exploren las opciones juntos. No se envía nada y no se inicia ninguna solicitud."},"sheetDone":{"en":"Done","es":"Listo"},"preferenceNotNowAnnounce":{"en":"Not choosing a payment option today. You can change this choice.","es":"Hoy no elegimos una forma de pago. Puedes cambiar esta opción."},"preferenceClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."},"howPromotional":{"en":"Promotional plans from a credit provider. Your Lacks specialist confirms the provider, which plans are available and their terms.","es":"Planes promocionales de un proveedor de crédito. Tu especialista de Lacks confirma el proveedor, qué planes están disponibles y sus términos."},"howInstallment":{"en":"Credit arranged for this purchase. The provider decides approval and sets the terms; your Lacks specialist confirms them.","es":"Crédito para esta compra. El proveedor decide la aprobación y fija los términos; tu especialista de Lacks los confirma."},"howMexico":{"en":"A credit program for purchases delivered to Mexico. Requirements and terms are reviewed with your Lacks specialist.","es":"Un programa de crédito para compras con entrega en México. Los requisitos y términos se revisan con tu especialista de Lacks."},"topicDue":{"en":"What is due today is confirmed in store. Depending on the option, it can include an upfront amount, tax and delivery.","es":"Lo que se paga hoy se confirma en la tienda. Según la opción, puede incluir un monto inicial, impuestos y entrega."},"topicSchedule":{"en":"How often you pay, and for how long, depends on the option. Current terms are confirmed in store.","es":"Con qué frecuencia pagas, y por cuánto tiempo, depende de la opción. Los términos actuales se confirman en la tienda."},"topicFull":{"en":"The full cost adds up everything paid over time, anything paid upfront, and tax, delivery and other charges. It is confirmed in store.","es":"El costo total suma todo lo que se paga con el tiempo, lo que se paga al inicio, e impuestos, entrega y otros cargos. Se confirma en la tienda."},"topicOwnership":{"en":"When the items become yours can differ between options, especially lease-to-own. Ownership terms are confirmed in store.","es":"El momento en que los artículos pasan a ser tuyos puede variar según la opción, sobre todo en el arrendamiento con opción a compra. Los términos de propiedad se confirman en la tienda."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6911,7 +6911,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"promotions":{"schemaVersion":1,"activeScenario":null,"allowedSourceHosts":["lacks.com"],"scenarios":{}},"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","surfaces":{"drawer":false,"sleepSystem":false},"allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"paymentPreferenceLabel":{"en":"Payment preference","es":"Preferencia de pago"},"preferenceNone":{"en":"Not selected","es":"Sin seleccionar"},"hideDetails":{"en":"Hide details","es":"Ocultar detalles"},"considerOption":{"en":"Consider this option","es":"Considerar esta opción"},"currentlyConsidering":{"en":"Currently considering ✓","es":"En consideración ✓"},"clearPreference":{"en":"Clear preference","es":"Quitar preferencia"},"preferenceNotNow":{"en":"Not choosing a payment option today","es":"Hoy no elegimos una forma de pago"},"exploreConsequence":{"en":"Explore options together. Nothing is submitted and no application is started.","es":"Exploren las opciones juntos. No se envía nada y no se inicia ninguna solicitud."},"sheetDone":{"en":"Done","es":"Listo"},"preferenceNotNowAnnounce":{"en":"Not choosing a payment option today. You can change this choice.","es":"Hoy no elegimos una forma de pago. Puedes cambiar esta opción."},"preferenceClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."},"howPromotional":{"en":"Promotional plans from a credit provider. Your Lacks specialist confirms the provider, which plans are available and their terms.","es":"Planes promocionales de un proveedor de crédito. Tu especialista de Lacks confirma el proveedor, qué planes están disponibles y sus términos."},"howInstallment":{"en":"Credit arranged for this purchase. The provider decides approval and sets the terms; your Lacks specialist confirms them.","es":"Crédito para esta compra. El proveedor decide la aprobación y fija los términos; tu especialista de Lacks los confirma."},"howMexico":{"en":"A credit program for purchases delivered to Mexico. Requirements and terms are reviewed with your Lacks specialist.","es":"Un programa de crédito para compras con entrega en México. Los requisitos y términos se revisan con tu especialista de Lacks."},"topicDue":{"en":"What is due today is confirmed in store. Depending on the option, it can include an upfront amount, tax and delivery.","es":"Lo que se paga hoy se confirma en la tienda. Según la opción, puede incluir un monto inicial, impuestos y entrega."},"topicSchedule":{"en":"How often you pay, and for how long, depends on the option. Current terms are confirmed in store.","es":"Con qué frecuencia pagas, y por cuánto tiempo, depende de la opción. Los términos actuales se confirman en la tienda."},"topicFull":{"en":"The full cost adds up everything paid over time, anything paid upfront, and tax, delivery and other charges. It is confirmed in store.","es":"El costo total suma todo lo que se paga con el tiempo, lo que se paga al inicio, e impuestos, entrega y otros cargos. Se confirma en la tienda."},"topicOwnership":{"en":"When the items become yours can differ between options, especially lease-to-own. Ownership terms are confirmed in store.","es":"El momento en que los artículos pasan a ser tuyos puede variar según la opción, sobre todo en el arrendamiento con opción a compra. Los términos de propiedad se confirman en la tienda."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
+          <t>{"promotions":{"schemaVersion":1,"activeScenario":null,"allowedSourceHosts":["lacks.com"],"scenarios":{}},"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-10-03T13:51:56-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","surfaces":{"drawer":false,"sleepSystem":false},"allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"paymentPreferenceLabel":{"en":"Payment preference","es":"Preferencia de pago"},"preferenceNone":{"en":"Not selected","es":"Sin seleccionar"},"hideDetails":{"en":"Hide details","es":"Ocultar detalles"},"considerOption":{"en":"Consider this option","es":"Considerar esta opción"},"currentlyConsidering":{"en":"Currently considering ✓","es":"En consideración ✓"},"clearPreference":{"en":"Clear preference","es":"Quitar preferencia"},"preferenceNotNow":{"en":"Not choosing a payment option today","es":"Hoy no elegimos una forma de pago"},"exploreConsequence":{"en":"Explore options together. Nothing is submitted and no application is started.","es":"Exploren las opciones juntos. No se envía nada y no se inicia ninguna solicitud."},"sheetDone":{"en":"Done","es":"Listo"},"preferenceNotNowAnnounce":{"en":"Not choosing a payment option today. You can change this choice.","es":"Hoy no elegimos una forma de pago. Puedes cambiar esta opción."},"preferenceClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."},"howPromotional":{"en":"Promotional plans from a credit provider. Your Lacks specialist confirms the provider, which plans are available and their terms.","es":"Planes promocionales de un proveedor de crédito. Tu especialista de Lacks confirma el proveedor, qué planes están disponibles y sus términos."},"howInstallment":{"en":"Credit arranged for this purchase. The provider decides approval and sets the terms; your Lacks specialist confirms them.","es":"Crédito para esta compra. El proveedor decide la aprobación y fija los términos; tu especialista de Lacks los confirma."},"howMexico":{"en":"A credit program for purchases delivered to Mexico. Requirements and terms are reviewed with your Lacks specialist.","es":"Un programa de crédito para compras con entrega en México. Los requisitos y términos se revisan con tu especialista de Lacks."},"topicDue":{"en":"What is due today is confirmed in store. Depending on the option, it can include an upfront amount, tax and delivery.","es":"Lo que se paga hoy se confirma en la tienda. Según la opción, puede incluir un monto inicial, impuestos y entrega."},"topicSchedule":{"en":"How often you pay, and for how long, depends on the option. Current terms are confirmed in store.","es":"Con qué frecuencia pagas, y por cuánto tiempo, depende de la opción. Los términos actuales se confirman en la tienda."},"topicFull":{"en":"The full cost adds up everything paid over time, anything paid upfront, and tax, delivery and other charges. It is confirmed in store.","es":"El costo total suma todo lo que se paga con el tiempo, lo que se paga al inicio, e impuestos, entrega y otros cargos. Se confirma en la tienda."},"topicOwnership":{"en":"When the items become yours can differ between options, especially lease-to-own. Ownership terms are confirmed in store.","es":"El momento en que los artículos pasan a ser tuyos puede variar según la opción, sobre todo en el arrendamiento con opción a compra. Los términos de propiedad se confirman en la tienda."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-10-03T13:51:56-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentRounding":"up-to-whole-dollar","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-10-03T13:51:56-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"published-equal-division","paymentRounding":"up-to-whole-dollar","downPaymentRequired":true,"chargesRequiredAtPurchase":true,"paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-10-03T13:51:56-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-10-03T13:51:56-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-10-03T13:51:56-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -5033,7 +5033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5074,80 +5074,85 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>SKUs by Size</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Description (ES)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Image File Name</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Match Tags</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Score: Default</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Score: Cooling</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Score: Hot</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Score: Back Pain</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Score: Snoring</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Score: Reflux</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Score: Premium</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Score: Position Side</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Score: Position Back</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Score: Position Stomach</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Score: Allergies</t>
         </is>
@@ -5185,35 +5190,33 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
         <v>899</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Adjustable power base with head &amp; foot articulation, wireless remote, and programmable memory positions.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Base eléctrica ajustable con elevación de cabeza y pies, control inalámbrico y posiciones de memoria programables.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>images/accessories/base-bt2000.jpg</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>snoring, reflux, back_pain</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>3</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>3</v>
       </c>
@@ -5221,12 +5224,15 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5260,48 +5266,49 @@
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
         <v>1099</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Adjustable base with head &amp; foot massage, 5 vibration modes, one-touch flat, and wireless remote with presets.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Base ajustable con masaje de cabeza y pies, 5 modos de vibración, regreso plano de un toque y control inalámbrico con posiciones predeterminadas.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>images/accessories/base-bt3000.jpg</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>snoring, reflux, back_pain</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
       </c>
       <c r="R3" t="n">
         <v>3</v>
       </c>
       <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
         <v>2</v>
       </c>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5335,35 +5342,33 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
         <v>1599</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Premium adjustable base with lumbar support and a virtually unlimited range of head &amp; foot positions, including Zero Gravity.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Base ajustable premium con soporte lumbar y un rango casi ilimitado de posiciones de cabeza y pies, incluida Gravedad Cero.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>images/accessories/base-tempur-ergo.jpg</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>snoring, reflux, back_pain</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>4</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>4</v>
       </c>
@@ -5371,12 +5376,15 @@
         <v>4</v>
       </c>
       <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5410,33 +5418,33 @@
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
         <v>499</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>9-inch wood foundation engineered to support your mattress edge to edge and extend its life.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Base de madera de 9 pulgadas diseñada para soportar tu colchón de borde a borde y extender su vida útil.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>images/accessories/foundation-princess.jpg</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>2</v>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -5446,6 +5454,7 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5475,48 +5484,49 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
         <v>108</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Performance pillow with a soft t-shirt-like cover and airflow design for cooler, better-supported sleep.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Almohada de alto rendimiento con funda suave tipo camiseta y diseño de ventilación para dormir más fresco y con mejor soporte.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>images/accessories/pillow-flow.jpg</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>cooling, hot_sleeper, all, all_positions</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
       <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5546,31 +5556,29 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
         <v>99</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Cool-gel memory foam that softens and adjusts to your neck, taking pressure off your spine without overheating.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Espuma viscoelástica con gel fresco que se suaviza y se ajusta a tu cuello, quitando presión de la columna sin sobrecalentarte.</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>images/accessories/pillow-gel-memory.jpg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>cooling, hot_sleeper, all, all_positions</t>
         </is>
-      </c>
-      <c r="M7" t="n">
-        <v>2</v>
       </c>
       <c r="N7" t="n">
         <v>2</v>
@@ -5578,16 +5586,19 @@
       <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="n">
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5617,44 +5628,45 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
         <v>149</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Moisture-wicking, breathable protection that keeps you dry and comfortable while guarding against spills.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Protección transpirable que absorbe la humedad, te mantiene seco y cómodo y protege contra derrames.</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>images/accessories/protector-dritec.jpg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>all, allergies, spills, everyday</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
-      <c r="W8" t="n">
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5686,33 +5698,33 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
         <v>89</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Simple, breathable everyday protection against spills and dust — comfort without compromise.</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Protección diaria sencilla y transpirable contra derrames y polvo — confort sin compromisos.</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>images/accessories/protector-iprotect.jpg</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>all, allergies, spills, everyday</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -5721,7 +5733,8 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5753,39 +5766,39 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
         <v>249</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Instant-cooling top fabric for hot sleepers, with a Powerband fit that guards against spills without changing the feel.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Tela superior de enfriamiento instantáneo para quienes duermen con calor, con ajuste Powerband que protege contra derrames sin cambiar la sensación.</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>images/accessories/protector-vertex.jpg</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>cooling, hot_sleeper, spills, everyday</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -5793,6 +5806,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5822,44 +5836,45 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
         <v>189</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Cooling, moisture-wicking protector with SurfaceGuard technology and a 10-year warranty.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Protector refrescante que absorbe la humedad, con tecnología SurfaceGuard y garantía de 10 años.</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>images/accessories/protector-tempur.jpg</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>all, allergies, spills, everyday</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="n">
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6967,7 +6982,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"pricing":{"schemaVersion":1,"enabled":false,"displayEnabled":false,"currency":"USD","authority":{"owner":"","role":""},"freshness":{"status":"unapproved","maxAgeDays":null,"approvedBy":"","approvedAt":null},"sourcePolicy":{"status":"unapproved","allowedSourceHosts":[],"approvedBy":"","approvedAt":null},"purchaseAssessment":{"policy":"runtime-transaction-amount"},"sizes":["twin","twin_xl","full","queen","king","cal_king"],"surfaces":{"drawer":false,"sleepSystem":false,"results":false,"handoff":false,"sleepPlan":false,"compare":false},"presentation":{"status":"unapproved","approvals":{"business":{"status":"unapproved","by":"","at":null},"legal":{"status":"unapproved","by":"","at":null},"nativeReview":{"status":"pending","by":"","at":null}},"assumptions":[],"disclosures":[],"states":{}},"products":[],"formulas":[]}}</t>
+          <t>{"pricing":{"schemaVersion":1,"enabled":false,"displayEnabled":false,"currency":"USD","authority":{"owner":"","role":""},"freshness":{"status":"unapproved","maxAgeDays":null,"approvedBy":"","approvedAt":null},"sourcePolicy":{"status":"unapproved","allowedSourceHosts":[],"approvedBy":"","approvedAt":null},"purchaseAssessment":{"policy":"runtime-transaction-amount"},"sizes":["twin","twin_xl","full","queen","king","cal_king"],"surfaces":{"drawer":false,"sleepSystem":false,"results":false,"handoff":false,"sleepPlan":false,"compare":false,"email":false},"presentation":{"status":"unapproved","approvals":{"business":{"status":"unapproved","by":"","at":null},"legal":{"status":"unapproved","by":"","at":null},"nativeReview":{"status":"pending","by":"","at":null}},"assumptions":[],"disclosures":[],"states":{}},"products":[],"formulas":[],"offers":[]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -14,7 +14,8 @@
     <sheet name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Promotions" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Quiz" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Pricing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Guide" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Pricing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6975,6 +6976,34 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Guide JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>{"customerPolicies":{"allowedSourceHosts":["lacks.com","www.lacks.com"],"comfortPromise":{"status":"draft","sourceUrl":"https://www.lacks.com/return-and-store-policies","verifiedAt":"2026-10-17","maxAgeDays":60,"spanishReview":"pending","approval":null,"title":{"en":"90-Day Comfort Promise","es":"Promesa de Comodidad de 90 Días"},"summary":{"en":"Lacks publishes a one-time comfort exchange for a new mattress, with conditions.","es":"Lacks publica un cambio único por comodidad para un colchón nuevo, con condiciones."},"timeline":{"minNights":30,"windowDays":90},"requiresProtector":true,"requiresPillow":true,"conditions":[{"en":"Sleep on the mattress for at least 30 nights, then request the exchange within 90 days of delivery.","es":"Duerme en el colchón al menos 30 noches y luego solicita el cambio dentro de los 90 días posteriores a la entrega."},{"en":"One exchange, for a mattress of equal or greater value. If the new mattress costs more, you pay the difference.","es":"Un solo cambio, por un colchón de igual o mayor valor. Si el nuevo colchón cuesta más, pagas la diferencia."},{"en":"The purchase must include a mattress protector and at least one pillow, and the mattress must have been used with that protector.","es":"La compra debe incluir un protector de colchón y al menos una almohada, y el colchón debe haberse usado con ese protector."},{"en":"The mattress must be in good condition, free of stains, odors or damage.","es":"El colchón debe estar en buen estado, sin manchas, olores ni daños."},{"en":"A local delivery fee applies to the exchange.","es":"El cambio está sujeto a un cargo de entrega local."},{"en":"This is an exchange, not a refund. Pillows and protectors cannot be refunded or exchanged.","es":"Es un cambio, no un reembolso. Las almohadas y los protectores no se reembolsan ni se cambian."},{"en":"Lacks authorizes and inspects every exchange. Items sold as clearance, as-is or final sale, and special-order merchandise, are listed as not eligible for exchange; your specialist confirms how this applies to your mattress.","es":"Lacks autoriza e inspecciona cada cambio. Los artículos vendidos en liquidación, tal como están o en venta final, y la mercancía de pedido especial, aparecen como no elegibles para cambio; tu especialista confirma cómo aplica esto a tu colchón."}],"takeHome":{"en":"One comfort exchange after 30 nights and within 90 days of delivery, with conditions; your specialist confirms qualification.","es":"Un cambio por comodidad después de 30 noches y dentro de los 90 días posteriores a la entrega, con condiciones; tu especialista confirma si aplica."}},"fulfillment":{"status":"draft","sourceUrl":"https://www.lacks.com/services","verifiedAt":"2026-10-17","maxAgeDays":60,"spanishReview":"pending","approval":null,"title":{"en":"Getting your new bed home","es":"Cómo llevar tu cama nueva a casa"},"intro":{"en":"Lacks publishes these ways to get your purchase home. Your specialist confirms what applies to your order.","es":"Lacks publica estas formas de llevar tu compra a casa. Tu especialista confirma lo que aplica a tu pedido."},"pickupNoCharge":true,"pickupChargeFact":{"status":"draft","approval":null},"deliveryLabel":{"en":"Delivery and setup","es":"Entrega e instalación"},"pickupLabel":{"en":"Warehouse pickup","es":"Recogida en almacén"},"deliveryNote":{"en":"Full-service delivery with in-home setup is published; its charge is confirmed in store.","es":"Se publica la entrega completa con instalación en casa; su cargo se confirma en la tienda."},"pickupNote":{"en":"Published as free from the central warehouse. Bring the sales contract and a matching photo ID.","es":"Se publica como gratuita en el almacén central. Lleva el contrato de venta y una identificación con foto que coincida."},"deliveryPoints":[{"en":"Brought inside, assembled and set up in the room you choose.","es":"Se lleva adentro, se arma y se instala en la habitación que elijas."},{"en":"Unboxed and inspected at the distribution center first.","es":"Primero se desempaca y se inspecciona en el centro de distribución."},{"en":"Clear the room and a path to it before the crew arrives.","es":"Despeja la habitación y el camino hacia ella antes de que llegue el equipo."},{"en":"Decorator services, such as making the bed, are not included.","es":"No incluye servicios de decoración, como tender la cama."}],"pickupPoints":[{"en":"Published at no additional cost from the Lacks central warehouse.","es":"Se publica sin costo adicional en el almacén central de Lacks."},{"en":"Bring a copy of your sales contract and a valid photo ID. The names must match.","es":"Lleva una copia de tu contrato de venta y una identificación con foto vigente. Los nombres deben coincidir."},{"en":"Someone else collecting needs Lacks' third-party waiver form, linked on lacks.com/services.","es":"Si otra persona recoge, necesita el formulario de autorización de terceros de Lacks, en lacks.com/services."}],"specialistConfirms":[{"en":"Delivery charge and coverage for your address","es":"El cargo de entrega y la cobertura para tu dirección"},{"en":"Delivery date or pickup readiness","es":"La fecha de entrega o cuándo estará listo para recoger"},{"en":"Whether removal of your old mattress is available","es":"Si se puede retirar tu colchón anterior"},{"en":"Whether setup of your bed base is included","es":"Si se incluye la instalación de tu base de cama"},{"en":"Warehouse location and hours","es":"La ubicación y el horario del almacén"}],"takeHome":{"en":"Delivery with in-home setup, or free warehouse pickup with your sales contract and a matching photo ID. Charges and dates are confirmed with your specialist.","es":"Entrega con instalación en casa, o recogida gratuita en el almacén con tu contrato de venta y una identificación con foto que coincida. Los cargos y las fechas se confirman con tu especialista."}},"afterPurchase":{"status":"draft","sourceUrl":"https://www.lacks.com/faq","verifiedAt":"2026-10-17","maxAgeDays":60,"spanishReview":"pending","approval":null,"title":{"en":"After your purchase","es":"Después de tu compra"},"body":{"en":"Questions after delivery or pickup? Contact your Lacks store, or use the service request on lacks.com.","es":"¿Preguntas después de la entrega o la recogida? Comunícate con tu tienda Lacks o usa la solicitud de servicio en lacks.com."},"links":[{"label":{"en":"Find your store","es":"Encuentra tu tienda"},"url":"https://www.lacks.com/contacts"},{"label":{"en":"Service request","es":"Solicitud de servicio"},"url":"https://www.lacks.com/services#service-form"}]},"mexicoDelivery":{"status":"draft","sourceUrl":"https://www.lacks.com/promotions/mexico-ads","verifiedAt":"2026-10-17","maxAgeDays":60,"spanishReview":"pending","approval":null,"title":{"en":"Delivering to Mexico","es":"Entrega en México"},"body":{"en":"Lacks publishes delivery to your door in Mexico through a professional import agent, for an additional charge. Coverage, cost and timing are confirmed with your specialist.","es":"Lacks publica la entrega hasta la puerta de tu hogar en México a través de un agente profesional de importación, con cargo adicional. La cobertura, el costo y los tiempos se confirman con tu especialista."},"points":[{"en":"Import of your purchase","es":"La importación de tu compra"},{"en":"Assembly and placement in your home","es":"El armado y el acomodo en tu hogar"},{"en":"Removal of leftover material","es":"El retiro del material sobrante"}],"note":{"en":"Delivery is separate from credit: it does not mean an order qualifies for any financing.","es":"La entrega es independiente del crédito: no significa que un pedido califique para algún financiamiento."}}},"productVisuals":[]}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>Pricing JSON</t>
         </is>
       </c>
